--- a/parameters/demand_parameters.xlsx
+++ b/parameters/demand_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aghil\Documents\MoFuSS_FAO_localhost\slv_bau_100m_ajustado\LULCC\DownloadedDatasets\SourceDataEl Salvador\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aghil\Documents\MoFuSS_FAO_localhost\ken_bau_1km_nv1\LULCC\DownloadedDatasets\SourceDataGlobal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14EA866-89E7-4693-852F-B3DE1C9357D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAA139A-6D53-4582-91E0-45DA5637D2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{119154BE-EFD1-4249-B324-41D845CFCB02}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{119154BE-EFD1-4249-B324-41D845CFCB02}"/>
   </bookViews>
   <sheets>
     <sheet name="share" sheetId="1" r:id="rId1"/>
@@ -729,9 +729,7 @@
       <c r="C6" s="7">
         <v>2012</v>
       </c>
-      <c r="D6" s="8">
-        <v>0.67275000000000007</v>
-      </c>
+      <c r="D6" s="8"/>
       <c r="E6" s="7"/>
       <c r="F6" s="8">
         <v>0.67275000000000007</v>
@@ -747,9 +745,7 @@
       <c r="C7" s="2">
         <v>2012</v>
       </c>
-      <c r="D7" s="3">
-        <v>0.252</v>
-      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="2"/>
       <c r="F7" s="3">
         <v>0.252</v>
@@ -765,9 +761,7 @@
       <c r="C8" s="4">
         <v>2012</v>
       </c>
-      <c r="D8" s="5">
-        <v>9.1000000000000004E-3</v>
-      </c>
+      <c r="D8" s="5"/>
       <c r="E8" s="4"/>
       <c r="F8" s="5">
         <v>9.1000000000000004E-3</v>
@@ -783,9 +777,7 @@
       <c r="C9" s="12">
         <v>2012</v>
       </c>
-      <c r="D9" s="13">
-        <v>6.2350000000000003E-2</v>
-      </c>
+      <c r="D9" s="13"/>
       <c r="E9" s="12"/>
       <c r="F9" s="13">
         <v>6.2350000000000003E-2</v>
@@ -857,9 +849,11 @@
       <c r="C14" s="7">
         <v>2050</v>
       </c>
-      <c r="D14" s="8"/>
+      <c r="D14" s="7">
+        <v>0.5</v>
+      </c>
       <c r="E14" s="7">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F14" s="8"/>
     </row>
@@ -873,9 +867,11 @@
       <c r="C15" s="2">
         <v>2050</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="2">
+        <v>0.01</v>
+      </c>
       <c r="E15" s="2">
-        <v>4.4101433296582096E-3</v>
+        <v>0.2</v>
       </c>
       <c r="F15" s="3"/>
     </row>
@@ -889,9 +885,11 @@
       <c r="C16" s="4">
         <v>2050</v>
       </c>
-      <c r="D16" s="5"/>
+      <c r="D16" s="4">
+        <v>0.4</v>
+      </c>
       <c r="E16" s="4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F16" s="5"/>
     </row>
@@ -905,9 +903,11 @@
       <c r="C17" s="12">
         <v>2050</v>
       </c>
-      <c r="D17" s="13"/>
+      <c r="D17" s="12">
+        <v>0.8</v>
+      </c>
       <c r="E17" s="12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F17" s="13"/>
     </row>
@@ -959,7 +959,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="15">
-        <f ca="1">H2</f>
+        <f>H2</f>
         <v>0.13760514596734291</v>
       </c>
       <c r="C2" t="s">
@@ -978,7 +978,7 @@
         <v>26</v>
       </c>
       <c r="H2" s="15">
-        <f ca="1">B$5*(D$5*F$5)/(D2*F2)</f>
+        <f>B$5*(D$5*F$5)/(D2*F2)</f>
         <v>0.13760514596734291</v>
       </c>
     </row>
@@ -987,7 +987,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="15">
-        <f t="shared" ref="B3:B7" ca="1" si="0">H3</f>
+        <f t="shared" ref="B3:B7" si="0">H3</f>
         <v>0.12359999999999999</v>
       </c>
       <c r="C3" t="s">
@@ -1006,7 +1006,7 @@
         <v>26</v>
       </c>
       <c r="H3" s="15">
-        <f ca="1">B$5*(D$5*F$5)/(D3*F3)</f>
+        <f>B$5*(D$5*F$5)/(D3*F3)</f>
         <v>0.12359999999999999</v>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="15">
-        <f ca="1">H4/1000</f>
+        <f>H4/1000</f>
         <v>1.1035714285714284</v>
       </c>
       <c r="C4" t="s">
@@ -1034,7 +1034,7 @@
         <v>26</v>
       </c>
       <c r="H4" s="15">
-        <f ca="1">B$5*(D$5*F$5)/(D4*F4)*1000</f>
+        <f>B$5*(D$5*F$5)/(D4*F4)*1000</f>
         <v>1103.5714285714284</v>
       </c>
     </row>
@@ -1043,7 +1043,6 @@
         <v>18</v>
       </c>
       <c r="B5" s="15">
-        <f t="shared" ca="1" si="0"/>
         <v>1.03</v>
       </c>
       <c r="C5" t="s">
@@ -1062,7 +1061,7 @@
         <v>27</v>
       </c>
       <c r="H5" s="15">
-        <f t="shared" ref="H5:H7" ca="1" si="1">B$5*(D$5*F$5)/(D5*F5)</f>
+        <f t="shared" ref="H5:H7" si="1">B$5*(D$5*F$5)/(D5*F5)</f>
         <v>1.03</v>
       </c>
     </row>
@@ -1071,7 +1070,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="15">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0.41199999999999998</v>
       </c>
       <c r="C6" t="s">
@@ -1090,7 +1089,7 @@
         <v>27</v>
       </c>
       <c r="H6" s="15">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>0.41199999999999998</v>
       </c>
       <c r="I6" s="18" t="s">
@@ -1102,7 +1101,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="16">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0.79005681818181805</v>
       </c>
       <c r="C7" s="14" t="s">
@@ -1121,7 +1120,7 @@
         <v>28</v>
       </c>
       <c r="H7" s="16">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>0.79005681818181805</v>
       </c>
       <c r="I7" s="14"/>
